--- a/Lab_4/data/partB/param_optimization_process/v100_k40_s200_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v100_k40_s200_results.xlsx
@@ -518,40 +518,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>3</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N2" t="n">
         <v>3</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -594,25 +594,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -652,16 +652,16 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -698,25 +698,25 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -729,43 +729,43 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
         <v>5</v>
@@ -778,43 +778,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>57</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>8</v>
+      </c>
+      <c r="N7" t="n">
         <v>6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>55</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>6</v>
-      </c>
-      <c r="N7" t="n">
-        <v>10</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -845,28 +845,28 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H8" t="n">
         <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
+        <v>9</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>5</v>
       </c>
-      <c r="L8" t="n">
-        <v>2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6</v>
-      </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -882,46 +882,46 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>52</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="n">
-        <v>53</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
         <v>4</v>
@@ -937,16 +937,16 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -995,16 +995,16 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>35</v>
@@ -1013,22 +1013,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1041,10 +1041,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1090,28 +1090,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1123,16 +1123,16 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1145,46 +1145,46 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G14" t="n">
         <v>5</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N14" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1200,13 +1200,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
@@ -1215,16 +1215,16 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
@@ -1233,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,49 +1246,49 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" t="n">
         <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" t="n">
         <v>5</v>
-      </c>
-      <c r="F16" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="n">
         <v>3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8016,7 +8016,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13711,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="C822" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="C1172" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21463,7 +21463,7 @@
       </c>
       <c r="C1186" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21514,7 +21514,7 @@
       </c>
       <c r="C1189" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21616,7 +21616,7 @@
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22636,7 +22636,7 @@
       </c>
       <c r="C1255" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23163,7 +23163,7 @@
       </c>
       <c r="C1286" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23180,7 +23180,7 @@
       </c>
       <c r="C1287" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23809,7 +23809,7 @@
       </c>
       <c r="C1324" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24217,7 +24217,7 @@
       </c>
       <c r="C1348" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -25271,7 +25271,7 @@
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25322,7 +25322,7 @@
       </c>
       <c r="C1413" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26104,7 +26104,7 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26325,7 +26325,7 @@
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
